--- a/p6_deployment/data/germany/missing/data_preparation/df_integrated_missing.xlsx
+++ b/p6_deployment/data/germany/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN42"/>
+  <dimension ref="A1:BN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54600</v>
+        <v>47000</v>
       </c>
       <c r="F2" t="n">
         <v>51500</v>
@@ -834,12 +834,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -883,22 +883,22 @@
         <v>73.36363636363636</v>
       </c>
       <c r="AI2" t="n">
-        <v>28.18181818181818</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.4545454545455</v>
+        <v>183.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.090909090909091</v>
+        <v>1.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>71.90909090909091</v>
+        <v>71.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>2870454.545454545</v>
+        <v>2857500</v>
       </c>
       <c r="AN2" t="n">
-        <v>73.72727272727273</v>
+        <v>73.8</v>
       </c>
       <c r="AO2" t="n">
         <v>24.08333333333333</v>
@@ -919,22 +919,22 @@
         <v>72.625</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.66666666666667</v>
+        <v>25.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>183.0952380952381</v>
+        <v>182.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.142857142857143</v>
+        <v>1.15</v>
       </c>
       <c r="AX2" t="n">
-        <v>70.66666666666667</v>
+        <v>70.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>3064285.714285714</v>
+        <v>3067500</v>
       </c>
       <c r="AZ2" t="n">
-        <v>74.38095238095238</v>
+        <v>74.45</v>
       </c>
       <c r="BA2" t="n">
         <v>19.5</v>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1085,22 +1085,22 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>28.09090909090909</v>
+        <v>27.88888888888889</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.4545454545455</v>
+        <v>181.8888888888889</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.181818181818182</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AF3" t="n">
-        <v>72.81818181818181</v>
+        <v>72.77777777777777</v>
       </c>
       <c r="AG3" t="n">
-        <v>3659090.909090909</v>
+        <v>3827777.777777778</v>
       </c>
       <c r="AH3" t="n">
-        <v>73.81818181818181</v>
+        <v>74</v>
       </c>
       <c r="AI3" t="n">
         <v>26.36363636363636</v>
@@ -1121,22 +1121,22 @@
         <v>73.36363636363636</v>
       </c>
       <c r="AO3" t="n">
-        <v>27.28571428571428</v>
+        <v>27.15</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.5238095238095</v>
+        <v>181.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.047619047619048</v>
+        <v>1.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>2392857.142857143</v>
+        <v>2362500</v>
       </c>
       <c r="AT3" t="n">
-        <v>73.95238095238095</v>
+        <v>74</v>
       </c>
       <c r="AU3" t="n">
         <v>23.29166666666667</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>hAcTWKK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2VSFgl3</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>185.6666666666667</v>
+        <v>184.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.777777777777778</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>81.11111111111111</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>31833333.33333333</v>
+        <v>35200000</v>
       </c>
       <c r="AH4" t="n">
-        <v>84.66666666666667</v>
+        <v>84.8</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1337,40 +1337,40 @@
         <v>76.72727272727273</v>
       </c>
       <c r="AO4" t="n">
-        <v>23.45454545454545</v>
+        <v>23.60869565217391</v>
       </c>
       <c r="AP4" t="n">
-        <v>182.5454545454545</v>
+        <v>182.0434782608696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.045454545454545</v>
+        <v>2.08695652173913</v>
       </c>
       <c r="AR4" t="n">
-        <v>80.09090909090909</v>
+        <v>80.34782608695652</v>
       </c>
       <c r="AS4" t="n">
-        <v>39372727.27272727</v>
+        <v>40508695.65217391</v>
       </c>
       <c r="AT4" t="n">
-        <v>84.59090909090909</v>
+        <v>84.65217391304348</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.57894736842105</v>
+        <v>23.61111111111111</v>
       </c>
       <c r="AV4" t="n">
-        <v>183.2631578947368</v>
+        <v>182.9444444444445</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.052631578947368</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX4" t="n">
-        <v>71.68421052631579</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AY4" t="n">
-        <v>5056578.947368421</v>
+        <v>5093055.555555556</v>
       </c>
       <c r="AZ4" t="n">
-        <v>77.47368421052632</v>
+        <v>77.38888888888889</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1380,25 +1380,25 @@
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>25.375</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="BI4" t="n">
-        <v>183.5</v>
+        <v>184.4285714285714</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.25</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="BK4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
-        <v>585</v>
+        <v>511</v>
       </c>
       <c r="BM4" t="n">
-        <v>37500000</v>
+        <v>31500000</v>
       </c>
       <c r="BN4" t="n">
-        <v>603</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81365</v>
+        <v>62000</v>
       </c>
       <c r="F5" t="n">
         <v>81365</v>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Q1njn0V</t>
+          <t>Q1njn0Vm</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>MDhPV0R</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1525,40 +1525,40 @@
         <v>83.72727272727273</v>
       </c>
       <c r="AI5" t="n">
-        <v>26.90909090909091</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>186.1818181818182</v>
+        <v>187.2</v>
       </c>
       <c r="AK5" t="n">
         <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>71.36363636363636</v>
+        <v>71.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>2606818.181818182</v>
+        <v>2517500</v>
       </c>
       <c r="AN5" t="n">
-        <v>74.09090909090909</v>
+        <v>74</v>
       </c>
       <c r="AO5" t="n">
-        <v>24.34782608695652</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AP5" t="n">
-        <v>184.0434782608696</v>
+        <v>184.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>1.958333333333333</v>
       </c>
       <c r="AR5" t="n">
-        <v>79.17391304347827</v>
+        <v>79</v>
       </c>
       <c r="AS5" t="n">
-        <v>26413043.47826087</v>
+        <v>25429166.66666667</v>
       </c>
       <c r="AT5" t="n">
-        <v>83.04347826086956</v>
+        <v>82.70833333333333</v>
       </c>
       <c r="AU5" t="n">
         <v>25.08695652173913</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58000</v>
+        <v>47000</v>
       </c>
       <c r="F6" t="n">
         <v>57500</v>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>UgdQz0f</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>pfoInmc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>24.81818181818182</v>
+        <v>24.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>183.5454545454545</v>
+        <v>183</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.818181818181818</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>16500000</v>
+        <v>16350000</v>
       </c>
       <c r="AH6" t="n">
-        <v>81.45454545454545</v>
+        <v>81.3</v>
       </c>
       <c r="AI6" t="n">
         <v>24.36363636363636</v>
@@ -1820,25 +1820,25 @@
         <v>315</v>
       </c>
       <c r="BH6" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>178</v>
+        <v>177.5</v>
       </c>
       <c r="BJ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK6" t="n">
         <v>2</v>
       </c>
-      <c r="BK6" t="n">
-        <v>3</v>
-      </c>
       <c r="BL6" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="BM6" t="n">
-        <v>82300000</v>
+        <v>31800000</v>
       </c>
       <c r="BN6" t="n">
-        <v>243</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>8W0vrAR</t>
+          <t>8W0vrAR9</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>lGJdeem</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>KUx4Q7x</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>CQTUFgP</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60449</v>
+        <v>54800</v>
       </c>
       <c r="F9" t="n">
         <v>60058</v>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>GzfvcwR</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>M5BRZDs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2397,58 +2397,58 @@
         <v>79.27272727272727</v>
       </c>
       <c r="AI9" t="n">
-        <v>25.5</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>184.3</v>
+        <v>184.1111111111111</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.6</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AL9" t="n">
-        <v>75.59999999999999</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="AM9" t="n">
-        <v>9700000</v>
+        <v>8388888.888888888</v>
       </c>
       <c r="AN9" t="n">
-        <v>78.8</v>
+        <v>78.55555555555556</v>
       </c>
       <c r="AO9" t="n">
-        <v>25.25</v>
+        <v>25.42857142857143</v>
       </c>
       <c r="AP9" t="n">
-        <v>183.0833333333333</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.291666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AR9" t="n">
-        <v>71.91666666666667</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="AS9" t="n">
-        <v>5502083.333333333</v>
+        <v>6045238.095238095</v>
       </c>
       <c r="AT9" t="n">
-        <v>75.08333333333333</v>
+        <v>75.52380952380952</v>
       </c>
       <c r="AU9" t="n">
-        <v>22.69565217391304</v>
+        <v>21.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>183.695652173913</v>
+        <v>184.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.304347826086957</v>
+        <v>1.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>69.56521739130434</v>
+        <v>69.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>4823913.043478261</v>
+        <v>5352500</v>
       </c>
       <c r="AZ9" t="n">
-        <v>78.21739130434783</v>
+        <v>79.45</v>
       </c>
       <c r="BA9" t="n">
         <v>21.2</v>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>v9WoiHG</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>l0fHXMd</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2649,22 +2649,22 @@
         <v>76.70833333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>26.16666666666667</v>
+        <v>26.10526315789474</v>
       </c>
       <c r="AV10" t="n">
-        <v>183.1666666666667</v>
+        <v>183.5263157894737</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.555555555555556</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="AX10" t="n">
-        <v>74.22222222222223</v>
+        <v>74.10526315789474</v>
       </c>
       <c r="AY10" t="n">
-        <v>6561111.111111111</v>
+        <v>6342105.263157895</v>
       </c>
       <c r="AZ10" t="n">
-        <v>76.22222222222223</v>
+        <v>76.15789473684211</v>
       </c>
       <c r="BA10" t="n">
         <v>29.75</v>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>4fuCGs9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -2833,22 +2833,22 @@
         <v>76.09090909090909</v>
       </c>
       <c r="AI11" t="n">
-        <v>27.72727272727273</v>
+        <v>27.44444444444444</v>
       </c>
       <c r="AJ11" t="n">
-        <v>185.9090909090909</v>
+        <v>184.8888888888889</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.181818181818182</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AL11" t="n">
-        <v>73.18181818181819</v>
+        <v>73.22222222222223</v>
       </c>
       <c r="AM11" t="n">
-        <v>3538636.363636364</v>
+        <v>3680555.555555556</v>
       </c>
       <c r="AN11" t="n">
-        <v>75.45454545454545</v>
+        <v>76</v>
       </c>
       <c r="AO11" t="n">
         <v>25.125</v>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>f3ddUIX</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>vZA6VYp</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="W12" t="n">
@@ -3107,25 +3107,25 @@
         <v>77.20833333333333</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="BB12" t="n">
-        <v>185</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>366</v>
+        <v>440</v>
       </c>
       <c r="BF12" t="n">
-        <v>50325000</v>
+        <v>55225000</v>
       </c>
       <c r="BG12" t="n">
-        <v>400</v>
+        <v>476</v>
       </c>
       <c r="BH12" t="n">
         <v>28</v>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>hAcTWKK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="W13" t="n">
@@ -3255,76 +3255,76 @@
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>28.81818181818182</v>
+        <v>28.77777777777778</v>
       </c>
       <c r="AD13" t="n">
-        <v>183</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.272727272727273</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF13" t="n">
-        <v>73.81818181818181</v>
+        <v>74</v>
       </c>
       <c r="AG13" t="n">
-        <v>3711363.636363636</v>
+        <v>3891666.666666667</v>
       </c>
       <c r="AH13" t="n">
-        <v>74.81818181818181</v>
+        <v>75.22222222222223</v>
       </c>
       <c r="AI13" t="n">
-        <v>25.36363636363636</v>
+        <v>25.9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>187.0909090909091</v>
+        <v>188.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.818181818181818</v>
+        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>79.45454545454545</v>
+        <v>80.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>23881818.18181818</v>
+        <v>25950000</v>
       </c>
       <c r="AN13" t="n">
-        <v>83.18181818181819</v>
+        <v>83.3</v>
       </c>
       <c r="AO13" t="n">
-        <v>26.23809523809524</v>
+        <v>25.94736842105263</v>
       </c>
       <c r="AP13" t="n">
-        <v>184.5714285714286</v>
+        <v>183.9473684210526</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.047619047619048</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AR13" t="n">
-        <v>71</v>
+        <v>70.78947368421052</v>
       </c>
       <c r="AS13" t="n">
-        <v>2526190.476190476</v>
+        <v>2486842.105263158</v>
       </c>
       <c r="AT13" t="n">
-        <v>74.0952380952381</v>
+        <v>74.21052631578948</v>
       </c>
       <c r="AU13" t="n">
-        <v>23.94117647058824</v>
+        <v>24.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>180.2352941176471</v>
+        <v>178.85</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.588235294117647</v>
+        <v>1.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>77.47058823529412</v>
+        <v>78.75</v>
       </c>
       <c r="AY13" t="n">
-        <v>25211764.70588235</v>
+        <v>31255000</v>
       </c>
       <c r="AZ13" t="n">
-        <v>83.11764705882354</v>
+        <v>83.55</v>
       </c>
       <c r="BA13" t="n">
         <v>26.83333333333333</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75024</v>
+        <v>66000</v>
       </c>
       <c r="F14" t="n">
         <v>75000</v>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>CQTUFgP</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>f3ddUIX</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>MDhPV0R</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>KUx4Q7x</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="W15" t="n">
@@ -3763,25 +3763,25 @@
         <v>78.625</v>
       </c>
       <c r="BA15" t="n">
-        <v>26.375</v>
+        <v>25.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>183.875</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="BC15" t="n">
         <v>1</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="BF15" t="n">
-        <v>17700000</v>
+        <v>12700000</v>
       </c>
       <c r="BG15" t="n">
-        <v>589</v>
+        <v>443</v>
       </c>
       <c r="BH15" t="n">
         <v>23.75</v>
@@ -3880,12 +3880,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>vZA6VYp</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Q1njn0V</t>
+          <t>Q1njn0Vm</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3929,22 +3929,22 @@
         <v>78.81818181818181</v>
       </c>
       <c r="AI16" t="n">
-        <v>24.2</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AJ16" t="n">
-        <v>183.7</v>
+        <v>184.7272727272727</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AL16" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="AM16" t="n">
-        <v>21930000</v>
+        <v>20190909.09090909</v>
       </c>
       <c r="AN16" t="n">
-        <v>82.59999999999999</v>
+        <v>81.90909090909091</v>
       </c>
       <c r="AO16" t="n">
         <v>25.14285714285714</v>
@@ -4100,12 +4100,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>M5BRZDs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>UgdQz0f</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -4131,58 +4131,58 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>25.27272727272727</v>
+        <v>25.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>184.5454545454545</v>
+        <v>184.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.636363636363636</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>76.18181818181819</v>
+        <v>75.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>10927272.72727273</v>
+        <v>9870000</v>
       </c>
       <c r="AH17" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>24.7</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AJ17" t="n">
-        <v>184.7</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.9</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AL17" t="n">
-        <v>78.3</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="AM17" t="n">
-        <v>17550000</v>
+        <v>17500000</v>
       </c>
       <c r="AN17" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="n">
-        <v>26.26086956521739</v>
+        <v>25.4</v>
       </c>
       <c r="AP17" t="n">
-        <v>182.695652173913</v>
+        <v>183.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.565217391304348</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>6639130.434782608</v>
+        <v>7440000</v>
       </c>
       <c r="AT17" t="n">
-        <v>76.34782608695652</v>
+        <v>77.3</v>
       </c>
       <c r="AU17" t="n">
         <v>23.57894736842105</v>
@@ -4203,25 +4203,25 @@
         <v>79.26315789473684</v>
       </c>
       <c r="BA17" t="n">
-        <v>25.33333333333333</v>
+        <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>185.6666666666667</v>
+        <v>183</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE17" t="n">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="BF17" t="n">
-        <v>16150000</v>
+        <v>12450000</v>
       </c>
       <c r="BG17" t="n">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="BH17" t="n">
         <v>24.2</v>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>50000</v>
+        <v>43000</v>
       </c>
       <c r="F18" t="n">
         <v>50000</v>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>lGJdeem</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>v9WoiHG</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="W18" t="n">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>l0fHXMd</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>4ljanuk</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -4599,22 +4599,22 @@
         <v>75.09090909090909</v>
       </c>
       <c r="AO19" t="n">
-        <v>25.72222222222222</v>
+        <v>25.68421052631579</v>
       </c>
       <c r="AP19" t="n">
-        <v>184.5555555555555</v>
+        <v>184.8421052631579</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="AR19" t="n">
-        <v>73.05555555555556</v>
+        <v>73</v>
       </c>
       <c r="AS19" t="n">
-        <v>5122222.222222222</v>
+        <v>4978947.368421053</v>
       </c>
       <c r="AT19" t="n">
-        <v>75.72222222222223</v>
+        <v>75.68421052631579</v>
       </c>
       <c r="AU19" t="n">
         <v>26.25</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>47069</v>
+        <v>40000</v>
       </c>
       <c r="F20" t="n">
         <v>47069</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>pfoInmc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>4fuCGs9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="W20" t="n">
@@ -4855,25 +4855,25 @@
         <v>74.78260869565217</v>
       </c>
       <c r="BA20" t="n">
-        <v>23.33333333333333</v>
+        <v>22.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>177.3333333333333</v>
+        <v>176.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE20" t="n">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="BF20" t="n">
-        <v>140000000</v>
+        <v>89500000</v>
       </c>
       <c r="BG20" t="n">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="BH20" t="n">
         <v>24.66666666666667</v>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2VSFgl3</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>GzfvcwR</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="W21" t="n">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>185.1818181818182</v>
+        <v>186</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.727272727272727</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>74.36363636363636</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>6445454.545454546</v>
+        <v>6490000</v>
       </c>
       <c r="AH21" t="n">
-        <v>76.81818181818181</v>
+        <v>76.8</v>
       </c>
       <c r="AI21" t="n">
         <v>24.09090909090909</v>
@@ -5035,40 +5035,40 @@
         <v>79.81818181818181</v>
       </c>
       <c r="AO21" t="n">
-        <v>23.38095238095238</v>
+        <v>23.36842105263158</v>
       </c>
       <c r="AP21" t="n">
-        <v>185.3333333333333</v>
+        <v>185.578947368421</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.095238095238095</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AR21" t="n">
-        <v>71.57142857142857</v>
+        <v>71.42105263157895</v>
       </c>
       <c r="AS21" t="n">
-        <v>4432142.857142857</v>
+        <v>4351315.789473685</v>
       </c>
       <c r="AT21" t="n">
-        <v>77.47619047619048</v>
+        <v>77.42105263157895</v>
       </c>
       <c r="AU21" t="n">
-        <v>24.28571428571428</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AV21" t="n">
-        <v>182.9047619047619</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.142857142857143</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX21" t="n">
-        <v>72.42857142857143</v>
+        <v>73</v>
       </c>
       <c r="AY21" t="n">
-        <v>5815476.19047619</v>
+        <v>6501388.888888889</v>
       </c>
       <c r="AZ21" t="n">
-        <v>76.04761904761905</v>
+        <v>76.72222222222223</v>
       </c>
       <c r="BA21" t="n">
         <v>25.16666666666667</v>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>zyLSrbZ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>zyLSrbZ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>WvI4Hnn</t>
+          <t>WvI4Hnn1</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>54600</v>
+        <v>47000</v>
       </c>
       <c r="F24" t="n">
         <v>50028</v>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>IgZoGKF</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -5561,22 +5561,22 @@
         <v>72.90909090909091</v>
       </c>
       <c r="AI24" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>179.8888888888889</v>
+        <v>179.7</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>68.66666666666667</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AM24" t="n">
-        <v>1994444.444444444</v>
+        <v>1465000</v>
       </c>
       <c r="AN24" t="n">
-        <v>71.44444444444444</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AO24" t="n">
         <v>24.375</v>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>8E8qmw3</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>OzPMRhK</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>8E86CPu</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>57274</v>
+        <v>49000</v>
       </c>
       <c r="F27" t="n">
         <v>55800</v>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>EDRZkDz</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>YmfcAeC</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>t0ZPdkU</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>A15eUM4</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>UyNNTYW</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0AI1QUJ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2BYSk4K</t>
+          <t>2BYSk4KO</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>SQrxFAM</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -6683,22 +6683,22 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>25.54545454545455</v>
+        <v>25.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>184.0909090909091</v>
+        <v>183.5</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>68.54545454545455</v>
+        <v>68.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1638636.363636364</v>
+        <v>1692500</v>
       </c>
       <c r="AH30" t="n">
-        <v>71.54545454545455</v>
+        <v>71.8</v>
       </c>
       <c r="AI30" t="n">
         <v>24.36363636363636</v>
@@ -6719,22 +6719,22 @@
         <v>71.72727272727273</v>
       </c>
       <c r="AO30" t="n">
-        <v>25.8695652173913</v>
+        <v>25.68181818181818</v>
       </c>
       <c r="AP30" t="n">
-        <v>182.7826086956522</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>67.52173913043478</v>
+        <v>67.45454545454545</v>
       </c>
       <c r="AS30" t="n">
-        <v>1417173.913043478</v>
+        <v>1431590.909090909</v>
       </c>
       <c r="AT30" t="n">
-        <v>70.26086956521739</v>
+        <v>70.31818181818181</v>
       </c>
       <c r="AU30" t="n">
         <v>26.29166666666667</v>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>v12aAJd</t>
+          <t>v12aAJdR</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -6903,22 +6903,22 @@
         <v>75.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>25.08333333333333</v>
+        <v>25.95238095238095</v>
       </c>
       <c r="AP31" t="n">
-        <v>184.4583333333333</v>
+        <v>182.952380952381</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>65.875</v>
+        <v>67.28571428571429</v>
       </c>
       <c r="AS31" t="n">
-        <v>1358333.333333333</v>
+        <v>1509523.809523809</v>
       </c>
       <c r="AT31" t="n">
-        <v>69.91666666666667</v>
+        <v>70.04761904761905</v>
       </c>
       <c r="AU31" t="n">
         <v>28.05263157894737</v>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>QHesBmS</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SQrxFAM</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="W33" t="n">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>OzPMRhK</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>t0ZPdkU</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="W34" t="n">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>QHesBmS</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="W35" t="n">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>A15eUM4</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>74667</v>
+        <v>71000</v>
       </c>
       <c r="F37" t="n">
         <v>67144</v>
@@ -7984,12 +7984,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>v12aAJd</t>
+          <t>v12aAJdR</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2BYSk4K</t>
+          <t>2BYSk4KO</t>
         </is>
       </c>
       <c r="W37" t="n">
@@ -8061,22 +8061,22 @@
         <v>73.30434782608695</v>
       </c>
       <c r="AU37" t="n">
-        <v>26.25</v>
+        <v>26.05263157894737</v>
       </c>
       <c r="AV37" t="n">
-        <v>182.2</v>
+        <v>181.7894736842105</v>
       </c>
       <c r="AW37" t="n">
         <v>1</v>
       </c>
       <c r="AX37" t="n">
-        <v>67.84999999999999</v>
+        <v>67.78947368421052</v>
       </c>
       <c r="AY37" t="n">
-        <v>1513500</v>
+        <v>1535263.157894737</v>
       </c>
       <c r="AZ37" t="n">
-        <v>71.15000000000001</v>
+        <v>71.26315789473684</v>
       </c>
       <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>YmfcAeC</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>8E8qmw3</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="W38" t="n">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>62271</v>
+        <v>50000</v>
       </c>
       <c r="F39" t="n">
         <v>61833</v>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>UyNNTYW</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="W39" t="n">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>IgZoGKF</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>8E86CPu</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="W40" t="n">
@@ -8575,22 +8575,22 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>24.77777777777778</v>
+        <v>25.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>181</v>
+        <v>180.7</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AG40" t="n">
-        <v>2066666.666666667</v>
+        <v>1530000</v>
       </c>
       <c r="AH40" t="n">
-        <v>72</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AI40" t="n">
         <v>24.27272727272727</v>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0AI1QUJ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>EDRZkDz</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -9035,6 +9035,208 @@
       <c r="BM42" t="inlineStr"/>
       <c r="BN42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>GfN42CgJ</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45437.625</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>74322</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M43" t="n">
+        <v>35</v>
+      </c>
+      <c r="N43" t="n">
+        <v>65</v>
+      </c>
+      <c r="O43" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="n">
+        <v>8</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>59</v>
+      </c>
+      <c r="X43" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>20232024</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>182.9090909090909</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1475000</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>44700000</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>26.34782608695652</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>180.4782608695652</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>68.34782608695652</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1621521.739130435</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>70.82608695652173</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>22.81818181818182</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>180.9090909090909</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>78.68181818181819</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>29159090.90909091</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>83.90909090909091</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>136</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>3125000</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>143</v>
+      </c>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
